--- a/isrcap_2025/coefficients_mediation.xlsx
+++ b/isrcap_2025/coefficients_mediation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\2024_within_fam_rge\isrcap_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370A9609-FF28-48ED-AAAF-957AE9AC67A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A0346D-3988-4A85-AC71-A0F8F376D259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="128">
   <si>
-    <t>PGS → W1 ASB</t>
-  </si>
-  <si>
     <t>Total PGS effect on Parent-P</t>
   </si>
   <si>
@@ -40,9 +37,6 @@
   </si>
   <si>
     <t>Total PGS effect on School</t>
-  </si>
-  <si>
-    <t>Total PGS effect on W3 ASB controlling for W1 ASB</t>
   </si>
   <si>
     <t>model</t>
@@ -374,33 +368,18 @@
     <t>-0.038 ~ 0.085</t>
   </si>
   <si>
-    <t xml:space="preserve">    PGS → W1 ASB → Parent-P</t>
-  </si>
-  <si>
     <t xml:space="preserve">    PGS → Parent-P</t>
   </si>
   <si>
-    <t xml:space="preserve">    PGS → W1 ASB → Parent-C</t>
-  </si>
-  <si>
     <t xml:space="preserve">    PGS → Parent-C</t>
   </si>
   <si>
-    <t xml:space="preserve">    PGS → W1 ASB → Peer</t>
-  </si>
-  <si>
     <t xml:space="preserve">    PGS → Peer</t>
   </si>
   <si>
-    <t xml:space="preserve">    PGS → W1 ASB → School</t>
-  </si>
-  <si>
     <t xml:space="preserve">    PGS → School</t>
   </si>
   <si>
-    <t xml:space="preserve">    All indirect effectsc via Parent-P</t>
-  </si>
-  <si>
     <t xml:space="preserve">    All indirect effects via Parent-C</t>
   </si>
   <si>
@@ -408,9 +387,6 @@
   </si>
   <si>
     <t xml:space="preserve">    All indirect effects via School</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    PGS → W3 ASB</t>
   </si>
   <si>
     <t>level</t>
@@ -419,6 +395,30 @@
   <si>
     <t>0.028 ~ 0.131</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PGS → W1 EXT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PGS → W1 EXT → Parent-P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PGS → W1 EXT → Parent-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PGS → W1 EXT → Peer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PGS → W1 EXT → School</t>
+  </si>
+  <si>
+    <t>Total PGS effect on W3 EXT controlling for W1 EXT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PGS → W3 EXT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    All indirect effects via Parent-P</t>
   </si>
 </sst>
 </file>
@@ -429,13 +429,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -744,1321 +744,1321 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E77"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="53.109375" customWidth="1"/>
-    <col min="2" max="3" width="15.88671875" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="53.08984375" customWidth="1"/>
+    <col min="2" max="3" width="15.90625" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>-5.3999999999999999E-2</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>-5.7000000000000002E-2</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>-1.9E-2</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15">
         <v>3.9E-2</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>2E-3</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18">
         <v>-1E-3</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
         <v>38</v>
-      </c>
-      <c r="D21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D24">
         <v>-4.3999999999999997E-2</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D25">
         <v>-4.2000000000000003E-2</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D27">
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D33">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D34">
         <v>-3.4000000000000002E-2</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D35">
         <v>-6.0000000000000001E-3</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D36">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D37">
         <v>-0.01</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D38">
         <v>-7.0000000000000001E-3</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D39">
         <v>-1.4E-2</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D43">
         <v>-5.5E-2</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E46" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D47">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="E47" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E48" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D49">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E49" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D50">
         <v>-1.9E-2</v>
       </c>
       <c r="E50" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D51" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E51" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D52">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E52" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D53">
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="E53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D54">
         <v>-1E-3</v>
       </c>
       <c r="E54" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D55">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="E55" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D56">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E56" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B58" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D58">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="E58" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="B59" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D59" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E59" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D61" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E61" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D62">
         <v>-2.7E-2</v>
       </c>
       <c r="E62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D63">
         <v>-4.2000000000000003E-2</v>
       </c>
       <c r="E63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D64" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E64" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D65">
         <v>-4.0000000000000001E-3</v>
       </c>
       <c r="E65" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E66" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B67" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D67" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E67" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B68" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D68">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="E68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D69" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E69" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B70" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E70" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B71" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D71">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E71" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D72">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="E72" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B73" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D73">
         <v>1.4E-2</v>
       </c>
       <c r="E73" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B74" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D74">
         <v>-1.0999999999999999E-2</v>
       </c>
       <c r="E74" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D75">
         <v>2E-3</v>
       </c>
       <c r="E75" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B76" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D76">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E76" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B77" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D77">
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="E77" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
